--- a/Data/Export/Common/Flag_旗帜.xlsx
+++ b/Data/Export/Common/Flag_旗帜.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E3908C-32E3-4E68-8E6D-21B14A144106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88F8274-CD3D-4CE6-8B53-D61AD93FE9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="1755" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flags" sheetId="36" r:id="rId1"/>
@@ -604,180 +604,181 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>#387800</t>
+  </si>
+  <si>
+    <t>#d00028</t>
+  </si>
+  <si>
+    <t>#8c6529</t>
+  </si>
+  <si>
+    <t>#200070</t>
+  </si>
+  <si>
+    <t>#5a5a5a</t>
+  </si>
+  <si>
+    <t>#20dedf</t>
+  </si>
+  <si>
+    <t>#dad23a</t>
+  </si>
+  <si>
+    <t>#f59bb1</t>
+  </si>
+  <si>
+    <t>#a0d387</t>
+  </si>
+  <si>
+    <t>#1e1e1e</t>
+  </si>
+  <si>
+    <t>#f26b20</t>
+  </si>
+  <si>
+    <t>#a285ac</t>
+  </si>
+  <si>
+    <t>#5b1646</t>
+  </si>
+  <si>
+    <t>#8f0017</t>
+  </si>
+  <si>
+    <t>#89c731</t>
+  </si>
+  <si>
+    <t>#c4437a</t>
+  </si>
+  <si>
+    <t>#8591b9</t>
+  </si>
+  <si>
+    <t>#c2df87</t>
+  </si>
+  <si>
+    <t>#009979</t>
+  </si>
+  <si>
+    <t>#463900</t>
+  </si>
+  <si>
+    <t>#423a80</t>
+  </si>
+  <si>
+    <t>#9c9c9c</t>
+  </si>
+  <si>
+    <t>#736441</t>
+  </si>
+  <si>
+    <t>#00538f</t>
+  </si>
+  <si>
+    <t>#aa2b4f</t>
+  </si>
+  <si>
+    <t>#f25e51</t>
+  </si>
+  <si>
+    <t>#fff987</t>
+  </si>
+  <si>
+    <t>#f79720</t>
+  </si>
+  <si>
+    <t>#a89770</t>
+  </si>
+  <si>
+    <t>#932b77</t>
+  </si>
+  <si>
+    <t>#770094</t>
+  </si>
+  <si>
+    <t>#86461e</t>
+  </si>
+  <si>
+    <t>#007150</t>
+  </si>
+  <si>
+    <t>#f69964</t>
+  </si>
+  <si>
+    <t>#12495c</t>
+  </si>
+  <si>
+    <t>#8980ab</t>
+  </si>
+  <si>
+    <t>#008ec3</t>
+  </si>
+  <si>
+    <t>#00a53c</t>
+  </si>
+  <si>
+    <t>#ef344f</t>
+  </si>
+  <si>
+    <t>#dbaf6c</t>
+  </si>
+  <si>
+    <t>#fff415</t>
+  </si>
+  <si>
+    <t>#80c987</t>
+  </si>
+  <si>
+    <t>#8debeb</t>
+  </si>
+  <si>
+    <t>#7fa5cb</t>
+  </si>
+  <si>
+    <t>#006fa8</t>
+  </si>
+  <si>
+    <t>#b86f0c</t>
+  </si>
+  <si>
+    <t>#6eb7a6</t>
+  </si>
+  <si>
+    <t>#20df20</t>
+  </si>
+  <si>
+    <t>#df20de</t>
+  </si>
+  <si>
+    <t>#8d861e</t>
+  </si>
+  <si>
+    <t>#33b437</t>
+  </si>
+  <si>
+    <t>#bd8cad</t>
+  </si>
+  <si>
+    <t>#ec917f</t>
+  </si>
+  <si>
+    <t>#c59d58</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>#2828e8</t>
-  </si>
-  <si>
-    <t>#387800</t>
-  </si>
-  <si>
-    <t>#d00028</t>
-  </si>
-  <si>
-    <t>#8c6529</t>
-  </si>
-  <si>
-    <t>#200070</t>
-  </si>
-  <si>
-    <t>#5a5a5a</t>
-  </si>
-  <si>
-    <t>#20dedf</t>
-  </si>
-  <si>
-    <t>#dad23a</t>
-  </si>
-  <si>
-    <t>#f59bb1</t>
-  </si>
-  <si>
-    <t>#a0d387</t>
-  </si>
-  <si>
-    <t>#1e1e1e</t>
-  </si>
-  <si>
-    <t>#f26b20</t>
-  </si>
-  <si>
-    <t>#a285ac</t>
-  </si>
-  <si>
-    <t>#5b1646</t>
-  </si>
-  <si>
-    <t>#8f0017</t>
-  </si>
-  <si>
-    <t>#89c731</t>
-  </si>
-  <si>
-    <t>#c4437a</t>
-  </si>
-  <si>
-    <t>#8591b9</t>
-  </si>
-  <si>
-    <t>#c2df87</t>
-  </si>
-  <si>
-    <t>#009979</t>
-  </si>
-  <si>
-    <t>#463900</t>
-  </si>
-  <si>
-    <t>#423a80</t>
-  </si>
-  <si>
-    <t>#9c9c9c</t>
-  </si>
-  <si>
-    <t>#736441</t>
-  </si>
-  <si>
-    <t>#00538f</t>
-  </si>
-  <si>
-    <t>#aa2b4f</t>
-  </si>
-  <si>
-    <t>#f25e51</t>
-  </si>
-  <si>
-    <t>#fff987</t>
-  </si>
-  <si>
-    <t>#f79720</t>
-  </si>
-  <si>
-    <t>#a89770</t>
-  </si>
-  <si>
-    <t>#932b77</t>
-  </si>
-  <si>
-    <t>#770094</t>
-  </si>
-  <si>
-    <t>#86461e</t>
-  </si>
-  <si>
-    <t>#007150</t>
-  </si>
-  <si>
-    <t>#f69964</t>
-  </si>
-  <si>
-    <t>#12495c</t>
-  </si>
-  <si>
-    <t>#8980ab</t>
-  </si>
-  <si>
-    <t>#008ec3</t>
-  </si>
-  <si>
-    <t>#00a53c</t>
-  </si>
-  <si>
-    <t>#ef344f</t>
-  </si>
-  <si>
-    <t>#dbaf6c</t>
-  </si>
-  <si>
-    <t>#fff415</t>
-  </si>
-  <si>
-    <t>#80c987</t>
-  </si>
-  <si>
-    <t>#8debeb</t>
-  </si>
-  <si>
-    <t>#7fa5cb</t>
-  </si>
-  <si>
-    <t>#006fa8</t>
-  </si>
-  <si>
-    <t>#b86f0c</t>
-  </si>
-  <si>
-    <t>#6eb7a6</t>
-  </si>
-  <si>
-    <t>#20df20</t>
-  </si>
-  <si>
-    <t>#df20de</t>
-  </si>
-  <si>
-    <t>#8d861e</t>
-  </si>
-  <si>
-    <t>#33b437</t>
-  </si>
-  <si>
-    <t>#bd8cad</t>
-  </si>
-  <si>
-    <t>#ec917f</t>
-  </si>
-  <si>
-    <t>#c59d58</t>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1383,10 +1384,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>179</v>
@@ -1411,13 +1409,13 @@
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>70</v>
@@ -1438,13 +1436,13 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>71</v>
@@ -1468,10 +1466,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>72</v>
@@ -1495,10 +1493,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>73</v>
@@ -1522,10 +1520,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>74</v>
@@ -1549,10 +1547,10 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>75</v>
@@ -1576,10 +1574,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>76</v>
@@ -1603,10 +1601,10 @@
         <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>77</v>
@@ -1630,10 +1628,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>78</v>
@@ -1657,10 +1655,10 @@
         <v>15</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>79</v>
@@ -1684,10 +1682,10 @@
         <v>16</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>80</v>
@@ -1711,10 +1709,10 @@
         <v>17</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>81</v>
@@ -1738,10 +1736,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>82</v>
@@ -1765,10 +1763,10 @@
         <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>83</v>
@@ -1792,10 +1790,10 @@
         <v>20</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>84</v>
@@ -1819,10 +1817,10 @@
         <v>21</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>85</v>
@@ -1846,10 +1844,10 @@
         <v>22</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>86</v>
@@ -1873,10 +1871,10 @@
         <v>23</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>87</v>
@@ -1900,10 +1898,10 @@
         <v>24</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>88</v>
@@ -1926,18 +1924,18 @@
       <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>130</v>
+      <c r="C25" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)</f>
-        <v>22,22,206</v>
+        <v>237,197,210</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="4"/>
@@ -1954,18 +1952,18 @@
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>131</v>
+      <c r="C26" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F26" s="2" t="str">
         <f t="shared" ref="F26:F59" ca="1" si="0">_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)&amp;","&amp;_xlfn.FLOOR.MATH(RAND()*255)</f>
-        <v>185,22,33</v>
+        <v>212,54,127</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="4"/>
@@ -1983,17 +1981,17 @@
         <v>27</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F27" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>193,72,70</v>
+        <v>148,61,33</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="4"/>
@@ -2011,17 +2009,17 @@
         <v>28</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F28" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>171,192,245</v>
+        <v>214,152,135</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="4"/>
@@ -2039,17 +2037,17 @@
         <v>29</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F29" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>32,120,141</v>
+        <v>121,5,50</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="4"/>
@@ -2067,17 +2065,17 @@
         <v>30</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F30" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>207,37,111</v>
+        <v>154,122,64</v>
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="4"/>
@@ -2095,17 +2093,17 @@
         <v>31</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>95</v>
       </c>
       <c r="F31" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>133,198,113</v>
+        <v>12,28,36</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="4"/>
@@ -2123,17 +2121,17 @@
         <v>32</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F32" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>80,171,44</v>
+        <v>138,189,150</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="4"/>
@@ -2151,17 +2149,17 @@
         <v>33</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>97</v>
       </c>
       <c r="F33" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13,149,215</v>
+        <v>144,204,127</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="4"/>
@@ -2178,18 +2176,18 @@
       <c r="B34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>139</v>
+      <c r="C34" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F34" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>55,98,38</v>
+        <v>161,37,89</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="4"/>
@@ -2207,17 +2205,17 @@
         <v>35</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>99</v>
       </c>
       <c r="F35" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>56,253,173</v>
+        <v>170,196,225</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="4"/>
@@ -2235,17 +2233,17 @@
         <v>36</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F36" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>88,206,208</v>
+        <v>30,247,8</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="4"/>
@@ -2263,17 +2261,17 @@
         <v>37</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>101</v>
       </c>
       <c r="F37" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>33,253,247</v>
+        <v>27,180,214</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -2290,17 +2288,17 @@
         <v>38</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>102</v>
       </c>
       <c r="F38" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>254,153,185</v>
+        <v>36,248,74</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="4"/>
@@ -2318,17 +2316,17 @@
         <v>39</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>103</v>
       </c>
       <c r="F39" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>208,207,215</v>
+        <v>73,163,222</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="4"/>
@@ -2346,17 +2344,17 @@
         <v>40</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F40" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>90,88,136</v>
+        <v>43,187,62</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="4"/>
@@ -2374,17 +2372,17 @@
         <v>41</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>105</v>
       </c>
       <c r="F41" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>15,43,104</v>
+        <v>240,158,233</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="4"/>
@@ -2402,17 +2400,17 @@
         <v>42</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>106</v>
       </c>
       <c r="F42" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>175,220,27</v>
+        <v>26,95,141</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="4"/>
@@ -2430,17 +2428,17 @@
         <v>43</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>107</v>
       </c>
       <c r="F43" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>213,195,46</v>
+        <v>200,1,144</v>
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="4"/>
@@ -2458,17 +2456,17 @@
         <v>44</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>108</v>
       </c>
       <c r="F44" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>232,84,171</v>
+        <v>177,19,146</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="4"/>
@@ -2486,17 +2484,17 @@
         <v>45</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>109</v>
       </c>
       <c r="F45" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>162,207,31</v>
+        <v>235,155,202</v>
       </c>
       <c r="I45" s="6"/>
       <c r="J45" s="4"/>
@@ -2514,17 +2512,17 @@
         <v>46</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>165</v>
       </c>
       <c r="F46" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>163,76,151</v>
+        <v>195,151,135</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="4"/>
@@ -2540,18 +2538,18 @@
       <c r="B47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>131</v>
+      <c r="C47" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>166</v>
       </c>
       <c r="F47" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>229,144,48</v>
+        <v>103,244,81</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
@@ -2563,17 +2561,17 @@
         <v>152</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>167</v>
       </c>
       <c r="F48" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>145,138,12</v>
+        <v>106,104,103</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
@@ -2585,17 +2583,17 @@
         <v>153</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>168</v>
       </c>
       <c r="F49" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>136,156,153</v>
+        <v>192,10,146</v>
       </c>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
@@ -2607,17 +2605,17 @@
         <v>154</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>169</v>
       </c>
       <c r="F50" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30,116,242</v>
+        <v>146,15,81</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -2629,17 +2627,17 @@
         <v>155</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>170</v>
       </c>
       <c r="F51" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>222,34,193</v>
+        <v>5,90,1</v>
       </c>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
@@ -2651,17 +2649,17 @@
         <v>156</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>171</v>
       </c>
       <c r="F52" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>228,169,205</v>
+        <v>168,198,203</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
@@ -2673,17 +2671,17 @@
         <v>157</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F53" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>21,228,138</v>
+        <v>55,151,78</v>
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
@@ -2695,17 +2693,17 @@
         <v>158</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F54" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>172,83,243</v>
+        <v>11,223,186</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
@@ -2716,18 +2714,18 @@
       <c r="B55" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>139</v>
+      <c r="C55" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F55" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>65,211,53</v>
+        <v>166,74,206</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
@@ -2739,17 +2737,17 @@
         <v>160</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>175</v>
       </c>
       <c r="F56" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>182,40,1</v>
+        <v>99,127,60</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
@@ -2761,17 +2759,17 @@
         <v>161</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>176</v>
       </c>
       <c r="F57" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>35,99,128</v>
+        <v>134,133,127</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
@@ -2783,17 +2781,17 @@
         <v>162</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>177</v>
       </c>
       <c r="F58" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>36,106,129</v>
+        <v>203,29,21</v>
       </c>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
@@ -2805,17 +2803,17 @@
         <v>163</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>178</v>
       </c>
       <c r="F59" s="2" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>46,176,241</v>
+        <v>170,134,201</v>
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
@@ -2826,8 +2824,11 @@
       <c r="B60" s="2" t="s">
         <v>164</v>
       </c>
+      <c r="C60" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="D60" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
